--- a/correlations/HI_tauc/spring_hysteresis_tauc.xlsx
+++ b/correlations/HI_tauc/spring_hysteresis_tauc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\correlations\HI_tauc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F2FA54-0B1E-4BBC-9302-CA1054AFA0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE56646-8088-4326-A4D1-2F0ADE0E82F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="586" xr2:uid="{867610DC-2157-4A8B-BAD4-C3624B9432BC}"/>
   </bookViews>
